--- a/tame_output/ON/bt/strategyON_20230813.xlsx
+++ b/tame_output/ON/bt/strategyON_20230813.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -763,11 +763,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,12 +776,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107.3%</t>
+          <t>107.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>103.2%</t>
+          <t>103.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140.0%</t>
+          <t>139.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-08-12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>134.5%</t>
+          <t>134.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1687"/>
+  <dimension ref="A1:G1688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40311,7 +40311,7 @@
         <v>45149</v>
       </c>
       <c r="B1687" t="n">
-        <v>2.885101320666294</v>
+        <v>2.885579016844725</v>
       </c>
       <c r="C1687" t="n">
         <v>2.990153375390339</v>
@@ -40327,6 +40327,29 @@
       </c>
       <c r="G1687" t="n">
         <v>4.292582359262085</v>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" s="2" t="n">
+        <v>45150</v>
+      </c>
+      <c r="B1688" t="n">
+        <v>2.886032386438556</v>
+      </c>
+      <c r="C1688" t="n">
+        <v>2.989821863634327</v>
+      </c>
+      <c r="D1688" t="n">
+        <v>1.541704973538273</v>
+      </c>
+      <c r="E1688" t="n">
+        <v>3.606147428735889</v>
+      </c>
+      <c r="F1688" t="n">
+        <v>2.170714973119575</v>
+      </c>
+      <c r="G1688" t="n">
+        <v>4.292250847506073</v>
       </c>
     </row>
   </sheetData>
